--- a/TAMU_SCSC_Faculty.xlsx
+++ b/TAMU_SCSC_Faculty.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Specialization</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>

--- a/TAMU_SCSC_Faculty.xlsx
+++ b/TAMU_SCSC_Faculty.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3126,6 +3126,17 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Lucas Gregory</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TAMU_SCSC_Faculty.xlsx
+++ b/TAMU_SCSC_Faculty.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3137,6 +3137,17 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ravinder Singh</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TAMU_SCSC_Faculty.xlsx
+++ b/TAMU_SCSC_Faculty.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3148,6 +3148,17 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Weston Floyd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TAMU_SCSC_Faculty.xlsx
+++ b/TAMU_SCSC_Faculty.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3159,6 +3159,17 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Tim Paape</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TAMU_SCSC_Faculty.xlsx
+++ b/TAMU_SCSC_Faculty.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3170,6 +3170,28 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Musfiq Salehin</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Carlos Vela Garcia</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TAMU_SCSC_Faculty.xlsx
+++ b/TAMU_SCSC_Faculty.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3192,6 +3192,17 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ellen Melson</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
